--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127325761</v>
+        <v>127325787</v>
       </c>
       <c r="B3" t="n">
         <v>98442</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564060</v>
+        <v>564054</v>
       </c>
       <c r="R3" t="n">
-        <v>6990776</v>
+        <v>6990795</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127325787</v>
+        <v>127325761</v>
       </c>
       <c r="B4" t="n">
         <v>98442</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564054</v>
+        <v>564060</v>
       </c>
       <c r="R4" t="n">
-        <v>6990795</v>
+        <v>6990776</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>

--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127325745</v>
       </c>
       <c r="B2" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127325787</v>
+        <v>127325761</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564054</v>
+        <v>564060</v>
       </c>
       <c r="R3" t="n">
-        <v>6990795</v>
+        <v>6990776</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127325761</v>
+        <v>127325787</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564060</v>
+        <v>564054</v>
       </c>
       <c r="R4" t="n">
-        <v>6990776</v>
+        <v>6990795</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -969,7 +969,7 @@
         <v>127325707</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127325729</v>
       </c>
       <c r="B6" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127325745</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127325761</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127325787</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127325707</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127325729</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1158,6 +1158,1004 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127668380</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98482</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kolbjännsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>564066</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6990705</v>
+      </c>
+      <c r="S7" t="n">
+        <v>30</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127664804</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98448</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kolbjännsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>564115</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6990652</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127664826</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stormyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>563683</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6991277</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127664840</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stormyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>563683</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6991277</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127664890</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kolbjännsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>563933</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6990892</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127664912</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kolbjännsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>564018</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6990756</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127664813</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kolbjännsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>564115</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6990652</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127664895</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98448</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kolbjännsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>563919</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6990940</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127664851</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57661</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stormyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>563691</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6991285</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127664797</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98448</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kolbjännsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>564096</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6990657</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127325745</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127325761</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127325787</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127325707</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127325729</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1257,45 +1257,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127664804</v>
+        <v>127664826</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>56844</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kolbjännsjön, Jmt</t>
+          <t>Stormyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564115</v>
+        <v>563683</v>
       </c>
       <c r="R8" t="n">
-        <v>6990652</v>
+        <v>6991277</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1354,49 +1358,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127664826</v>
+        <v>127664804</v>
       </c>
       <c r="B9" t="n">
-        <v>56844</v>
+        <v>98448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stormyrberget, Jmt</t>
+          <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563683</v>
+        <v>564115</v>
       </c>
       <c r="R9" t="n">
-        <v>6991277</v>
+        <v>6990652</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1761,49 +1761,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127664813</v>
+        <v>127664895</v>
       </c>
       <c r="B13" t="n">
-        <v>56844</v>
+        <v>98448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564115</v>
+        <v>563919</v>
       </c>
       <c r="R13" t="n">
-        <v>6990652</v>
+        <v>6990940</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1862,45 +1858,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127664895</v>
+        <v>127664813</v>
       </c>
       <c r="B14" t="n">
-        <v>98448</v>
+        <v>56844</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563919</v>
+        <v>564115</v>
       </c>
       <c r="R14" t="n">
-        <v>6990940</v>
+        <v>6990652</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>

--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -1257,49 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127664826</v>
+        <v>127664804</v>
       </c>
       <c r="B8" t="n">
-        <v>56844</v>
+        <v>98448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stormyrberget, Jmt</t>
+          <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563683</v>
+        <v>564115</v>
       </c>
       <c r="R8" t="n">
-        <v>6991277</v>
+        <v>6990652</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1358,45 +1354,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127664804</v>
+        <v>127664826</v>
       </c>
       <c r="B9" t="n">
-        <v>98448</v>
+        <v>56844</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kolbjännsjön, Jmt</t>
+          <t>Stormyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564115</v>
+        <v>563683</v>
       </c>
       <c r="R9" t="n">
-        <v>6990652</v>
+        <v>6991277</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>

--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127325745</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127325761</v>
       </c>
       <c r="B3" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127325787</v>
       </c>
       <c r="B4" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127325707</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127325729</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127668380</v>
       </c>
       <c r="B7" t="n">
-        <v>98482</v>
+        <v>98484</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,45 +1257,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127664804</v>
+        <v>127664826</v>
       </c>
       <c r="B8" t="n">
-        <v>98448</v>
+        <v>56846</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kolbjännsjön, Jmt</t>
+          <t>Stormyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564115</v>
+        <v>563683</v>
       </c>
       <c r="R8" t="n">
-        <v>6990652</v>
+        <v>6991277</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1354,49 +1358,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127664826</v>
+        <v>127664804</v>
       </c>
       <c r="B9" t="n">
-        <v>56844</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stormyrberget, Jmt</t>
+          <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563683</v>
+        <v>564115</v>
       </c>
       <c r="R9" t="n">
-        <v>6991277</v>
+        <v>6990652</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1458,7 +1458,7 @@
         <v>127664840</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>127664890</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>127664912</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>127664895</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>127664813</v>
       </c>
       <c r="B14" t="n">
-        <v>56844</v>
+        <v>56846</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>127664851</v>
       </c>
       <c r="B15" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>127664797</v>
       </c>
       <c r="B16" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -1761,45 +1761,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127664895</v>
+        <v>127664813</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>56846</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563919</v>
+        <v>564115</v>
       </c>
       <c r="R13" t="n">
-        <v>6990940</v>
+        <v>6990652</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1858,49 +1862,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127664813</v>
+        <v>127664895</v>
       </c>
       <c r="B14" t="n">
-        <v>56846</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564115</v>
+        <v>563919</v>
       </c>
       <c r="R14" t="n">
-        <v>6990652</v>
+        <v>6990940</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>

--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127325745</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127325761</v>
       </c>
       <c r="B3" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127325787</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127325707</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127325729</v>
       </c>
       <c r="B6" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127668380</v>
       </c>
       <c r="B7" t="n">
-        <v>98484</v>
+        <v>98490</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>127664804</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>127664895</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>127664797</v>
       </c>
       <c r="B16" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2155,6 +2155,223 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127929062</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kolbjännsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>564210</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6990588</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127929014</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57663</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kolbjännsjötorpet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>564176</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6990639</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127325745</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127325761</v>
       </c>
       <c r="B3" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127325787</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127325707</v>
       </c>
       <c r="B5" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127325729</v>
       </c>
       <c r="B6" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127668380</v>
       </c>
       <c r="B7" t="n">
-        <v>98490</v>
+        <v>98493</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127664826</v>
       </c>
       <c r="B8" t="n">
-        <v>56846</v>
+        <v>56849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>127664804</v>
       </c>
       <c r="B9" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>127664840</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>127664890</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>127664912</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>127664813</v>
       </c>
       <c r="B13" t="n">
-        <v>56846</v>
+        <v>56849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>127664895</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>127664851</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>127664797</v>
       </c>
       <c r="B16" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>127929062</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>127929014</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127325745</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127325761</v>
       </c>
       <c r="B3" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127325787</v>
       </c>
       <c r="B4" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127325707</v>
       </c>
       <c r="B5" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127325729</v>
       </c>
       <c r="B6" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127668380</v>
       </c>
       <c r="B7" t="n">
-        <v>98493</v>
+        <v>98501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127664826</v>
       </c>
       <c r="B8" t="n">
-        <v>56849</v>
+        <v>56855</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>127664804</v>
       </c>
       <c r="B9" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>127664840</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>127664890</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>127664912</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>127664813</v>
       </c>
       <c r="B13" t="n">
-        <v>56849</v>
+        <v>56855</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>127664895</v>
       </c>
       <c r="B14" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>127664851</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>127664797</v>
       </c>
       <c r="B16" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>127929062</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>127929014</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127325745</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127325761</v>
       </c>
       <c r="B3" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127325787</v>
       </c>
       <c r="B4" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127325707</v>
       </c>
       <c r="B5" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127325729</v>
       </c>
       <c r="B6" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127668380</v>
       </c>
       <c r="B7" t="n">
-        <v>98501</v>
+        <v>98502</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>127664804</v>
       </c>
       <c r="B9" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1761,49 +1761,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127664813</v>
+        <v>127664895</v>
       </c>
       <c r="B13" t="n">
-        <v>56855</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564115</v>
+        <v>563919</v>
       </c>
       <c r="R13" t="n">
-        <v>6990652</v>
+        <v>6990940</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1862,45 +1858,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127664895</v>
+        <v>127664813</v>
       </c>
       <c r="B14" t="n">
-        <v>98467</v>
+        <v>56855</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563919</v>
+        <v>564115</v>
       </c>
       <c r="R14" t="n">
-        <v>6990940</v>
+        <v>6990652</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2064,7 +2064,7 @@
         <v>127664797</v>
       </c>
       <c r="B16" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127325761</v>
+        <v>127325787</v>
       </c>
       <c r="B3" t="n">
         <v>98468</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564060</v>
+        <v>564054</v>
       </c>
       <c r="R3" t="n">
-        <v>6990776</v>
+        <v>6990795</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127325787</v>
+        <v>127325761</v>
       </c>
       <c r="B4" t="n">
         <v>98468</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564054</v>
+        <v>564060</v>
       </c>
       <c r="R4" t="n">
-        <v>6990795</v>
+        <v>6990776</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1257,49 +1257,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127664826</v>
+        <v>127664804</v>
       </c>
       <c r="B8" t="n">
-        <v>56855</v>
+        <v>98468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stormyrberget, Jmt</t>
+          <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563683</v>
+        <v>564115</v>
       </c>
       <c r="R8" t="n">
-        <v>6991277</v>
+        <v>6990652</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1358,45 +1354,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127664804</v>
+        <v>127664826</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>56855</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kolbjännsjön, Jmt</t>
+          <t>Stormyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564115</v>
+        <v>563683</v>
       </c>
       <c r="R9" t="n">
-        <v>6990652</v>
+        <v>6991277</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1761,45 +1761,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127664895</v>
+        <v>127664813</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>56855</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563919</v>
+        <v>564115</v>
       </c>
       <c r="R13" t="n">
-        <v>6990940</v>
+        <v>6990652</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1858,49 +1862,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127664813</v>
+        <v>127664895</v>
       </c>
       <c r="B14" t="n">
-        <v>56855</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564115</v>
+        <v>563919</v>
       </c>
       <c r="R14" t="n">
-        <v>6990652</v>
+        <v>6990940</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>

--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127325745</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127325787</v>
+        <v>127325761</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564054</v>
+        <v>564060</v>
       </c>
       <c r="R3" t="n">
-        <v>6990795</v>
+        <v>6990776</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127325761</v>
+        <v>127325787</v>
       </c>
       <c r="B4" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564060</v>
+        <v>564054</v>
       </c>
       <c r="R4" t="n">
-        <v>6990776</v>
+        <v>6990795</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -969,7 +969,7 @@
         <v>127325707</v>
       </c>
       <c r="B5" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127325729</v>
       </c>
       <c r="B6" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127668380</v>
       </c>
       <c r="B7" t="n">
-        <v>98502</v>
+        <v>98503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127664804</v>
       </c>
       <c r="B8" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1761,49 +1761,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127664813</v>
+        <v>127664895</v>
       </c>
       <c r="B13" t="n">
-        <v>56855</v>
+        <v>98469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564115</v>
+        <v>563919</v>
       </c>
       <c r="R13" t="n">
-        <v>6990652</v>
+        <v>6990940</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1862,45 +1858,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127664895</v>
+        <v>127664813</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>56855</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563919</v>
+        <v>564115</v>
       </c>
       <c r="R14" t="n">
-        <v>6990940</v>
+        <v>6990652</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2064,7 +2064,7 @@
         <v>127664797</v>
       </c>
       <c r="B16" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>127668380</v>
       </c>
       <c r="B7" t="n">
-        <v>98503</v>
+        <v>98504</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,45 +1257,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127664804</v>
+        <v>127664826</v>
       </c>
       <c r="B8" t="n">
-        <v>98469</v>
+        <v>56855</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kolbjännsjön, Jmt</t>
+          <t>Stormyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564115</v>
+        <v>563683</v>
       </c>
       <c r="R8" t="n">
-        <v>6990652</v>
+        <v>6991277</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1354,49 +1358,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127664826</v>
+        <v>127664804</v>
       </c>
       <c r="B9" t="n">
-        <v>56855</v>
+        <v>98470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stormyrberget, Jmt</t>
+          <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563683</v>
+        <v>564115</v>
       </c>
       <c r="R9" t="n">
-        <v>6991277</v>
+        <v>6990652</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1761,45 +1761,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127664895</v>
+        <v>127664813</v>
       </c>
       <c r="B13" t="n">
-        <v>98469</v>
+        <v>56855</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563919</v>
+        <v>564115</v>
       </c>
       <c r="R13" t="n">
-        <v>6990940</v>
+        <v>6990652</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1858,49 +1862,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127664813</v>
+        <v>127664895</v>
       </c>
       <c r="B14" t="n">
-        <v>56855</v>
+        <v>98470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564115</v>
+        <v>563919</v>
       </c>
       <c r="R14" t="n">
-        <v>6990652</v>
+        <v>6990940</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2064,7 +2064,7 @@
         <v>127664797</v>
       </c>
       <c r="B16" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -1761,49 +1761,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127664813</v>
+        <v>127664895</v>
       </c>
       <c r="B13" t="n">
-        <v>56855</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564115</v>
+        <v>563919</v>
       </c>
       <c r="R13" t="n">
-        <v>6990652</v>
+        <v>6990940</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1862,45 +1858,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127664895</v>
+        <v>127664813</v>
       </c>
       <c r="B14" t="n">
-        <v>98470</v>
+        <v>56855</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>563919</v>
+        <v>564115</v>
       </c>
       <c r="R14" t="n">
-        <v>6990940</v>
+        <v>6990652</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>

--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>127668380</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>98512</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>127664804</v>
       </c>
       <c r="B9" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>127664840</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         <v>127664890</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>127664912</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>127664895</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>127664851</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         <v>127664797</v>
       </c>
       <c r="B16" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>127929062</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>127929014</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -2161,7 +2161,7 @@
         <v>127929062</v>
       </c>
       <c r="B17" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>127929014</v>
       </c>
       <c r="B18" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -2161,7 +2161,7 @@
         <v>127929062</v>
       </c>
       <c r="B17" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>127929014</v>
       </c>
       <c r="B18" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127325745</v>
+        <v>127668380</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>98512</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564051</v>
+        <v>564066</v>
       </c>
       <c r="R2" t="n">
-        <v>6990780</v>
+        <v>6990705</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,45 +772,49 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127325761</v>
+        <v>127664826</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>56855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kolbjännsjön, Jmt</t>
+          <t>Stormyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564060</v>
+        <v>563683</v>
       </c>
       <c r="R3" t="n">
-        <v>6990776</v>
+        <v>6991277</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -837,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127325787</v>
+        <v>127664804</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>98478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564054</v>
+        <v>564115</v>
       </c>
       <c r="R4" t="n">
-        <v>6990795</v>
+        <v>6990652</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -934,12 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,48 +970,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127325707</v>
+        <v>127664840</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>57673</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kolbjännsjön, Jmt</t>
+          <t>Stormyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564066</v>
+        <v>563683</v>
       </c>
       <c r="R5" t="n">
-        <v>6990705</v>
+        <v>6991277</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1031,12 +1035,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,32 +1072,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127325729</v>
+        <v>127664890</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>57673</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,13 +1107,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564054</v>
+        <v>563933</v>
       </c>
       <c r="R6" t="n">
-        <v>6990764</v>
+        <v>6990892</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1128,12 +1137,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,32 +1174,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127668380</v>
+        <v>127664912</v>
       </c>
       <c r="B7" t="n">
-        <v>98512</v>
+        <v>57673</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,13 +1209,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564066</v>
+        <v>564018</v>
       </c>
       <c r="R7" t="n">
-        <v>6990705</v>
+        <v>6990756</v>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1231,6 +1245,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,49 +1276,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127664826</v>
+        <v>127664895</v>
       </c>
       <c r="B8" t="n">
-        <v>56855</v>
+        <v>98478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stormyrberget, Jmt</t>
+          <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563683</v>
+        <v>563919</v>
       </c>
       <c r="R8" t="n">
-        <v>6991277</v>
+        <v>6990940</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1358,35 +1373,39 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127664804</v>
+        <v>127664813</v>
       </c>
       <c r="B9" t="n">
-        <v>98478</v>
+        <v>56855</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kolbjännsjön, Jmt</t>
@@ -1455,7 +1474,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127664840</v>
+        <v>127664851</v>
       </c>
       <c r="B10" t="n">
         <v>57673</v>
@@ -1490,10 +1509,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563683</v>
+        <v>563691</v>
       </c>
       <c r="R10" t="n">
-        <v>6991277</v>
+        <v>6991285</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1557,32 +1576,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127664890</v>
+        <v>127664797</v>
       </c>
       <c r="B11" t="n">
-        <v>57673</v>
+        <v>98478</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,13 +1611,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563933</v>
+        <v>564096</v>
       </c>
       <c r="R11" t="n">
-        <v>6990892</v>
+        <v>6990657</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1628,11 +1647,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1659,10 +1673,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127664912</v>
+        <v>127929062</v>
       </c>
       <c r="B12" t="n">
-        <v>57673</v>
+        <v>57689</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1688,16 +1702,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564018</v>
+        <v>564210</v>
       </c>
       <c r="R12" t="n">
-        <v>6990756</v>
+        <v>6990588</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1724,17 +1743,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1761,45 +1780,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127664895</v>
+        <v>127929014</v>
       </c>
       <c r="B13" t="n">
-        <v>98478</v>
+        <v>57689</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kolbjännsjön, Jmt</t>
+          <t>Kolbjännsjötorpet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563919</v>
+        <v>564176</v>
       </c>
       <c r="R13" t="n">
-        <v>6990940</v>
+        <v>6990639</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1826,12 +1853,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1855,523 +1887,6 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>127664813</v>
-      </c>
-      <c r="B14" t="n">
-        <v>56855</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>102612</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Järpe</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Kolbjännsjön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>564115</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6990652</v>
-      </c>
-      <c r="S14" t="n">
-        <v>20</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Håsjö</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Joel Olsson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Joel Olsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>127664851</v>
-      </c>
-      <c r="B15" t="n">
-        <v>57673</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Stormyrberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>563691</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6991285</v>
-      </c>
-      <c r="S15" t="n">
-        <v>20</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Håsjö</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Joel Olsson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Joel Olsson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>127664797</v>
-      </c>
-      <c r="B16" t="n">
-        <v>98478</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Kolbjännsjön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>564096</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6990657</v>
-      </c>
-      <c r="S16" t="n">
-        <v>20</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Håsjö</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Joel Olsson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Joel Olsson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>127929062</v>
-      </c>
-      <c r="B17" t="n">
-        <v>57689</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Kolbjännsjön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>564210</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6990588</v>
-      </c>
-      <c r="S17" t="n">
-        <v>20</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Håsjö</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Joel Olsson</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Joel Olsson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>127929014</v>
-      </c>
-      <c r="B18" t="n">
-        <v>57689</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Kolbjännsjötorpet, Jmt</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>564176</v>
-      </c>
-      <c r="R18" t="n">
-        <v>6990639</v>
-      </c>
-      <c r="S18" t="n">
-        <v>20</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Bräcke</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Håsjö</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Joel Olsson</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Joel Olsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127668380</v>
+        <v>127325745</v>
       </c>
       <c r="B2" t="n">
-        <v>98512</v>
+        <v>98469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564066</v>
+        <v>564051</v>
       </c>
       <c r="R2" t="n">
-        <v>6990705</v>
+        <v>6990780</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,49 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127664826</v>
+        <v>127325761</v>
       </c>
       <c r="B3" t="n">
-        <v>56855</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stormyrberget, Jmt</t>
+          <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563683</v>
+        <v>564060</v>
       </c>
       <c r="R3" t="n">
-        <v>6991277</v>
+        <v>6990776</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -841,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127664804</v>
+        <v>127325787</v>
       </c>
       <c r="B4" t="n">
-        <v>98478</v>
+        <v>98469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564115</v>
+        <v>564054</v>
       </c>
       <c r="R4" t="n">
-        <v>6990652</v>
+        <v>6990795</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -938,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -970,48 +966,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127664840</v>
+        <v>127325707</v>
       </c>
       <c r="B5" t="n">
-        <v>57673</v>
+        <v>98469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stormyrberget, Jmt</t>
+          <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563683</v>
+        <v>564066</v>
       </c>
       <c r="R5" t="n">
-        <v>6991277</v>
+        <v>6990705</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1035,17 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1072,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127664890</v>
+        <v>127325729</v>
       </c>
       <c r="B6" t="n">
-        <v>57673</v>
+        <v>98469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1107,13 +1098,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563933</v>
+        <v>564054</v>
       </c>
       <c r="R6" t="n">
-        <v>6990892</v>
+        <v>6990764</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1137,17 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1174,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127664912</v>
+        <v>127668380</v>
       </c>
       <c r="B7" t="n">
-        <v>57673</v>
+        <v>98512</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,13 +1195,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564018</v>
+        <v>564066</v>
       </c>
       <c r="R7" t="n">
-        <v>6990756</v>
+        <v>6990705</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1276,45 +1257,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127664895</v>
+        <v>127664826</v>
       </c>
       <c r="B8" t="n">
-        <v>98478</v>
+        <v>56855</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kolbjännsjön, Jmt</t>
+          <t>Stormyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563919</v>
+        <v>563683</v>
       </c>
       <c r="R8" t="n">
-        <v>6990940</v>
+        <v>6991277</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1373,39 +1358,35 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127664813</v>
+        <v>127664804</v>
       </c>
       <c r="B9" t="n">
-        <v>56855</v>
+        <v>98478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kolbjännsjön, Jmt</t>
@@ -1474,7 +1455,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127664851</v>
+        <v>127664840</v>
       </c>
       <c r="B10" t="n">
         <v>57673</v>
@@ -1509,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563691</v>
+        <v>563683</v>
       </c>
       <c r="R10" t="n">
-        <v>6991285</v>
+        <v>6991277</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1576,32 +1557,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127664797</v>
+        <v>127664890</v>
       </c>
       <c r="B11" t="n">
-        <v>98478</v>
+        <v>57673</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1611,13 +1592,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>564096</v>
+        <v>563933</v>
       </c>
       <c r="R11" t="n">
-        <v>6990657</v>
+        <v>6990892</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1647,6 +1628,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1673,10 +1659,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127929062</v>
+        <v>127664912</v>
       </c>
       <c r="B12" t="n">
-        <v>57689</v>
+        <v>57673</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1702,21 +1688,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564210</v>
+        <v>564018</v>
       </c>
       <c r="R12" t="n">
-        <v>6990588</v>
+        <v>6990756</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1743,17 +1724,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1780,53 +1761,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127929014</v>
+        <v>127664895</v>
       </c>
       <c r="B13" t="n">
-        <v>57689</v>
+        <v>98478</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kolbjännsjötorpet, Jmt</t>
+          <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564176</v>
+        <v>563919</v>
       </c>
       <c r="R13" t="n">
-        <v>6990639</v>
+        <v>6990940</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1853,17 +1826,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1887,6 +1855,523 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127664813</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56855</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kolbjännsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>564115</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6990652</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127664851</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stormyrberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>563691</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6991285</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127664797</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98478</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kolbjännsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>564096</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6990657</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127929062</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kolbjännsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>564210</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6990588</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127929014</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57689</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kolbjännsjötorpet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>564176</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6990639</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Håsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joel Olsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127325745</v>
+        <v>127664840</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kolbjännsjön, Jmt</t>
+          <t>Stormyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564051</v>
+        <v>563683</v>
       </c>
       <c r="R2" t="n">
-        <v>6990780</v>
+        <v>6991277</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -740,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,45 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127325761</v>
+        <v>127664851</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kolbjännsjön, Jmt</t>
+          <t>Stormyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564060</v>
+        <v>563691</v>
       </c>
       <c r="R3" t="n">
-        <v>6990776</v>
+        <v>6991285</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -837,12 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127325787</v>
+        <v>127664880</v>
       </c>
       <c r="B4" t="n">
-        <v>98469</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,13 +914,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564054</v>
+        <v>563933</v>
       </c>
       <c r="R4" t="n">
-        <v>6990795</v>
+        <v>6990892</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -934,12 +944,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,32 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127325707</v>
+        <v>127664912</v>
       </c>
       <c r="B5" t="n">
-        <v>98469</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,13 +1016,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564066</v>
+        <v>564018</v>
       </c>
       <c r="R5" t="n">
-        <v>6990705</v>
+        <v>6990756</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1031,12 +1046,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,45 +1083,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127325729</v>
+        <v>127929014</v>
       </c>
       <c r="B6" t="n">
-        <v>98469</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kolbjännsjön, Jmt</t>
+          <t>Kolbjännsjötorpet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>564054</v>
+        <v>564176</v>
       </c>
       <c r="R6" t="n">
-        <v>6990764</v>
+        <v>6990639</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1128,12 +1156,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,48 +1193,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127668380</v>
+        <v>127929062</v>
       </c>
       <c r="B7" t="n">
-        <v>98512</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564066</v>
+        <v>564210</v>
       </c>
       <c r="R7" t="n">
-        <v>6990705</v>
+        <v>6990588</v>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1225,12 +1263,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,14 +1300,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127664826</v>
+        <v>127664813</v>
       </c>
       <c r="B8" t="n">
-        <v>56855</v>
+        <v>57132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1292,14 +1335,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stormyrberget, Jmt</t>
+          <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563683</v>
+        <v>564115</v>
       </c>
       <c r="R8" t="n">
-        <v>6991277</v>
+        <v>6990652</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1358,45 +1401,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127664804</v>
+        <v>127664826</v>
       </c>
       <c r="B9" t="n">
-        <v>98478</v>
+        <v>57132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kolbjännsjön, Jmt</t>
+          <t>Stormyrberget, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>564115</v>
+        <v>563683</v>
       </c>
       <c r="R9" t="n">
-        <v>6990652</v>
+        <v>6991277</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1455,48 +1502,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127664840</v>
+        <v>127668380</v>
       </c>
       <c r="B10" t="n">
-        <v>57673</v>
+        <v>99153</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stormyrberget, Jmt</t>
+          <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563683</v>
+        <v>564066</v>
       </c>
       <c r="R10" t="n">
-        <v>6991277</v>
+        <v>6990705</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1526,11 +1573,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1557,32 +1599,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127664890</v>
+        <v>127325707</v>
       </c>
       <c r="B11" t="n">
-        <v>57673</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,13 +1634,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563933</v>
+        <v>564066</v>
       </c>
       <c r="R11" t="n">
-        <v>6990892</v>
+        <v>6990705</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1622,17 +1664,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1659,32 +1696,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127664912</v>
+        <v>127325729</v>
       </c>
       <c r="B12" t="n">
-        <v>57673</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1694,10 +1731,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>564018</v>
+        <v>564054</v>
       </c>
       <c r="R12" t="n">
-        <v>6990756</v>
+        <v>6990764</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1724,17 +1761,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1761,10 +1793,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127664895</v>
+        <v>127325745</v>
       </c>
       <c r="B13" t="n">
-        <v>98478</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1796,10 +1828,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563919</v>
+        <v>564051</v>
       </c>
       <c r="R13" t="n">
-        <v>6990940</v>
+        <v>6990780</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1826,12 +1858,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1858,49 +1890,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127664813</v>
+        <v>127325761</v>
       </c>
       <c r="B14" t="n">
-        <v>56855</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564115</v>
+        <v>564060</v>
       </c>
       <c r="R14" t="n">
-        <v>6990652</v>
+        <v>6990776</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1927,12 +1955,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1959,45 +1987,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127664851</v>
+        <v>127325787</v>
       </c>
       <c r="B15" t="n">
-        <v>57673</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stormyrberget, Jmt</t>
+          <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>563691</v>
+        <v>564054</v>
       </c>
       <c r="R15" t="n">
-        <v>6991285</v>
+        <v>6990795</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2024,17 +2052,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2064,7 +2087,7 @@
         <v>127664797</v>
       </c>
       <c r="B16" t="n">
-        <v>98478</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2158,50 +2181,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127929062</v>
+        <v>127664804</v>
       </c>
       <c r="B17" t="n">
-        <v>57689</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564210</v>
+        <v>564115</v>
       </c>
       <c r="R17" t="n">
-        <v>6990588</v>
+        <v>6990652</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2228,17 +2246,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2265,53 +2278,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127929014</v>
+        <v>127664895</v>
       </c>
       <c r="B18" t="n">
-        <v>57689</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kolbjännsjötorpet, Jmt</t>
+          <t>Kolbjännsjön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564176</v>
+        <v>563919</v>
       </c>
       <c r="R18" t="n">
-        <v>6990639</v>
+        <v>6990940</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2338,17 +2343,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 10543-2022 artfynd.xlsx
+++ b/artfynd/A 10543-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127664840</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127664851</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127664880</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127664912</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127664826</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127668380</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127325707</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1472,6 +1512,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127325729</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1569,6 +1614,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127325745</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1666,6 +1716,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127325761</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1763,6 +1818,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127325787</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1860,6 +1920,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127664895</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1970,6 +2035,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127929014</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2077,6 +2147,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127929062</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2178,6 +2253,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127664813</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2275,6 +2355,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127664797</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2372,8 +2457,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127664804</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>